--- a/Design/config/CityBuildingConfig.xlsx
+++ b/Design/config/CityBuildingConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -89,14 +89,6 @@
     <t>ButtonGate</t>
   </si>
   <si>
-    <t>防御</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>集市</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -110,6 +102,26 @@
   </si>
   <si>
     <t>gate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>army</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ButtonArmy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>军营</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>城墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农田</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -578,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -589,10 +601,10 @@
         <v>20002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>16</v>
@@ -600,19 +612,33 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <v>20004</v>
+        <v>20003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>20004</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="A5:Q43">

--- a/Design/config/CityBuildingConfig.xlsx
+++ b/Design/config/CityBuildingConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -122,6 +122,18 @@
   </si>
   <si>
     <t>农田</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>house</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ButtonHouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>议事厅</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -517,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -640,6 +652,20 @@
         <v>19</v>
       </c>
     </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>20005</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A5:Q43">
     <sortCondition ref="A41"/>
